--- a/artfynd/A 29344-2021 artfynd.xlsx
+++ b/artfynd/A 29344-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29344-2021 artfynd.xlsx
+++ b/artfynd/A 29344-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91991639</v>
+        <v>92223669</v>
       </c>
       <c r="B2" t="n">
         <v>93235</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Munkedal, Boh</t>
+          <t>Munkedal, Dingle, Örekilsberget, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>307119.40395111</v>
+        <v>307118.8822583323</v>
       </c>
       <c r="R2" t="n">
-        <v>6500152.931453353</v>
+        <v>6500152.957280941</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +757,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Validerad av Lars Hedenäs.</t>
+          <t>Återfynd.  Tidigare rapporterad av Emma Enfjäll 2021-03-30.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -816,34 +816,24 @@
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Lars Hedenäs</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Ulf Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Ulf Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92223669</v>
+        <v>92200013</v>
       </c>
       <c r="B3" t="n">
-        <v>93235</v>
+        <v>95157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -856,49 +846,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>1590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Munkedal, Dingle, Örekilsberget, Boh</t>
+          <t>Munkedal, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>307118.8822583323</v>
+        <v>307101.6708271437</v>
       </c>
       <c r="R3" t="n">
-        <v>6500152.957280941</v>
+        <v>6500101.085388951</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -922,27 +907,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Återfynd.  Tidigare rapporterad av Emma Enfjäll 2021-03-30.</t>
+          <t>Surdråg med klibbal i brant blandskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -951,176 +936,26 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog i branter</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granlåga i sent nedbrytningsstadium</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga i sent nedbrytningsstadium</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulf Persson</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulf Persson</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>92200013</v>
-      </c>
-      <c r="B4" t="n">
-        <v>95157</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1590</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dunmossa</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Trichocolea tomentella</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ehrh.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Munkedal, Boh</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>307101.6708271437</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6500101.085388951</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Munkedal</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Svarteborg</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-03-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-03-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Surdråg med klibbal i brant blandskog.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blandskog i branter</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Emma Enfjäll</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Emma Enfjäll</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
